--- a/docs/downloads/04/tbl_origine_alaotra_analamiranga.xlsx
+++ b/docs/downloads/04/tbl_origine_alaotra_analamiranga.xlsx
@@ -397,12 +397,6 @@
           <t>Mpihavy</t>
         </is>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>8.699999999999999</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,12 +528,6 @@
         <is>
           <t>Valivotaka</t>
         </is>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>9.1</v>
       </c>
     </row>
     <row r="9">
